--- a/artfynd/A 12863-2024 artfynd.xlsx
+++ b/artfynd/A 12863-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109734916</v>
+        <v>109867535</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527503.9183500354</v>
+        <v>527515</v>
       </c>
       <c r="R2" t="n">
-        <v>6983577.603844037</v>
+        <v>6983326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109867535</v>
+        <v>109734952</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527515.1505068287</v>
+        <v>527411</v>
       </c>
       <c r="R3" t="n">
-        <v>6983325.782444254</v>
+        <v>6983537</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,22 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109867546</v>
+        <v>109867540</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527450.1479100552</v>
+        <v>527536</v>
       </c>
       <c r="R4" t="n">
-        <v>6983312.046985611</v>
+        <v>6983312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,19 +948,9 @@
           <t>2023-06-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109867540</v>
+        <v>109734916</v>
       </c>
       <c r="B5" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1503</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527536.2113685808</v>
+        <v>527504</v>
       </c>
       <c r="R5" t="n">
-        <v>6983312.318041531</v>
+        <v>6983578</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,22 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,16 +1082,11 @@
         <v>109867537</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1182,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527542.0655076932</v>
+        <v>527542</v>
       </c>
       <c r="R6" t="n">
-        <v>6983320.098095477</v>
+        <v>6983320</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,19 +1150,9 @@
           <t>2023-06-06</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,6 +1177,208 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>109867546</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gårdsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>527450</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6983312</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>109734923</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gårdsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>527480</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6983555</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12863-2024 artfynd.xlsx
+++ b/artfynd/A 12863-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109867535</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109734952</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109867540</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109734916</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109867537</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109867546</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,8 +1414,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109734923</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>